--- a/trunk/plan/excel/道具表.xlsx
+++ b/trunk/plan/excel/道具表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="20685" windowHeight="7260"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>SubType</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -50,30 +53,27 @@
     <t>Price</t>
   </si>
   <si>
-    <t>EffectIds</t>
+    <t>SkillId</t>
   </si>
   <si>
     <t>Quality</t>
   </si>
   <si>
-    <t>SubType</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>生命药水</t>
   </si>
   <si>
     <t>消耗品</t>
   </si>
   <si>
+    <t>药品</t>
+  </si>
+  <si>
     <t>恢复少量生命值</t>
   </si>
   <si>
@@ -86,9 +86,6 @@
     <t>普通</t>
   </si>
   <si>
-    <t>药品</t>
-  </si>
-  <si>
     <t>魔法药水</t>
   </si>
   <si>
@@ -107,19 +104,16 @@
     <t>装备</t>
   </si>
   <si>
+    <t>武器</t>
+  </si>
+  <si>
     <t>传说中的神兵利器</t>
   </si>
   <si>
     <t>item_sword_legend</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>传说</t>
-  </si>
-  <si>
-    <t>武器</t>
   </si>
 </sst>
 </file>
@@ -132,14 +126,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,148 +582,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1091,7 +1078,7 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="6" max="6" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1143,16 +1130,16 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
@@ -1163,31 +1150,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>99</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1195,31 +1182,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4">
+        <v>99</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="F4">
-        <v>99</v>
-      </c>
-      <c r="G4">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1227,31 +1214,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>9999</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
         <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
